--- a/data/reports/trongkhaithac-2025.xlsx
+++ b/data/reports/trongkhaithac-2025.xlsx
@@ -8,13 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\phuc8\Desktop\wildlife-backend\data\reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{27C11FC7-9F3C-4FB9-94A9-293EAF66A1CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A1F932F-9FD0-4629-9249-9540914CB48D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{BFD969C4-AD8A-4C3D-A5C8-AB189FA20CF5}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{BFD969C4-AD8A-4C3D-A5C8-AB189FA20CF5}"/>
   </bookViews>
   <sheets>
-    <sheet name="khaithac" sheetId="2" r:id="rId1"/>
-    <sheet name="trong" sheetId="1" r:id="rId2"/>
+    <sheet name="trongrung" sheetId="1" r:id="rId1"/>
+    <sheet name="khaithac" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -550,6 +550,123 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37A2E7D8-94C0-4D60-BF57-CAF3B34802E4}">
+  <dimension ref="A1:I4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="49.21875" customWidth="1"/>
+    <col min="3" max="3" width="23.109375" customWidth="1"/>
+    <col min="4" max="4" width="31.109375" customWidth="1"/>
+    <col min="5" max="5" width="18.44140625" customWidth="1"/>
+    <col min="6" max="6" width="19.5546875" customWidth="1"/>
+    <col min="7" max="7" width="15.109375" customWidth="1"/>
+    <col min="8" max="8" width="13.5546875" customWidth="1"/>
+    <col min="9" max="9" width="41.44140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G2" s="2">
+        <v>2025</v>
+      </c>
+      <c r="H2" s="2">
+        <v>5</v>
+      </c>
+      <c r="I2" s="2"/>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A3" s="2">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G3" s="2">
+        <v>2025</v>
+      </c>
+      <c r="H3" s="2">
+        <v>10</v>
+      </c>
+      <c r="I3" s="2"/>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A4" s="2"/>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2">
+        <v>15</v>
+      </c>
+      <c r="I4" s="2"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8433375F-2A4C-413F-93ED-B459C09C3A40}">
   <dimension ref="A1:J4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -680,121 +797,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37A2E7D8-94C0-4D60-BF57-CAF3B34802E4}">
-  <dimension ref="A1:I4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="49.21875" customWidth="1"/>
-    <col min="3" max="3" width="23.109375" customWidth="1"/>
-    <col min="4" max="4" width="31.109375" customWidth="1"/>
-    <col min="5" max="5" width="18.44140625" customWidth="1"/>
-    <col min="6" max="6" width="19.5546875" customWidth="1"/>
-    <col min="7" max="7" width="15.109375" customWidth="1"/>
-    <col min="8" max="8" width="13.5546875" customWidth="1"/>
-    <col min="9" max="9" width="41.44140625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A2" s="2">
-        <v>1</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G2" s="2">
-        <v>2025</v>
-      </c>
-      <c r="H2" s="2">
-        <v>5</v>
-      </c>
-      <c r="I2" s="2"/>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A3" s="2">
-        <v>2</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G3" s="2">
-        <v>2025</v>
-      </c>
-      <c r="H3" s="2">
-        <v>10</v>
-      </c>
-      <c r="I3" s="2"/>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A4" s="2"/>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2">
-        <v>15</v>
-      </c>
-      <c r="I4" s="2"/>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="4" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>